--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,24 +8395,24 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91620</v>
+        <v>91611</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>233197</v>
+        <v>233195</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria subtilis</t>
+          <t>Ramaria neoformosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Coker) Schild, 1982</t>
+          <t>sensu Schild</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Konsulterat och skickat kollekt till JO Hermansson. Sveaskogs naturvärdesinventering.</t>
+          <t>Konsulterat Martin Axegård via foton. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91613</v>
+        <v>91615</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91615</v>
+        <v>91616</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91616</v>
+        <v>91622</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91628</v>
+        <v>91641</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91641</v>
+        <v>91643</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91643</v>
+        <v>91646</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91646</v>
+        <v>91656</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91656</v>
+        <v>91657</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91657</v>
+        <v>91660</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91662</v>
+        <v>91667</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91667</v>
+        <v>91679</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91679</v>
+        <v>91680</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91680</v>
+        <v>91683</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91683</v>
+        <v>91687</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
